--- a/Retailer_Summary.xlsx
+++ b/Retailer_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>45.95650666666668</v>
+        <v>41.80709333333333</v>
       </c>
     </row>
     <row r="3">
@@ -508,7 +508,7 @@
         <v>19.66666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>27.61830333333333</v>
+        <v>28.76989666666667</v>
       </c>
     </row>
     <row r="4">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19.66666666666667</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>25.18221333333333</v>
+        <v>27.05408666666667</v>
       </c>
     </row>
     <row r="5">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>130.3228366666667</v>
+        <v>101.9920266666667</v>
       </c>
     </row>
     <row r="6">
@@ -592,39 +592,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30.66666666666667</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>23.48239</v>
+        <v>38.77142</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>2002057</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Supreme Traders (Badlapur)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>200205700618</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>JAGNATH MART</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>SHUBHANGI RAIKWAR</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>4.365593333333333</v>
+        <v>9.672739999999999</v>
       </c>
     </row>
     <row r="8">
@@ -650,10 +636,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>14.33333333333333</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>71.79268666666667</v>
+        <v>55.74277666666666</v>
       </c>
     </row>
     <row r="9">
@@ -679,10 +665,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16.33333333333333</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>45.28932666666666</v>
+        <v>31.40123333333334</v>
       </c>
     </row>
     <row r="10">
@@ -708,10 +694,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36.33333333333334</v>
+        <v>50.66666666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>476.4744699999999</v>
+        <v>345.4742133333334</v>
       </c>
     </row>
     <row r="11">
@@ -737,10 +723,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24.66666666666667</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>94.13180666666666</v>
+        <v>93.09971666666667</v>
       </c>
     </row>
     <row r="12">
@@ -766,10 +752,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>37</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>215.3770366666666</v>
+        <v>200.62471</v>
       </c>
     </row>
     <row r="13">
@@ -795,10 +781,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14.66666666666667</v>
+        <v>34.33333333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>162.8990033333334</v>
+        <v>171.3441033333334</v>
       </c>
     </row>
     <row r="14">
@@ -824,10 +810,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>35.66666666666666</v>
+        <v>47.33333333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>137.5717666666667</v>
+        <v>181.2304066666667</v>
       </c>
     </row>
     <row r="15">
@@ -853,10 +839,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>33.66666666666666</v>
       </c>
       <c r="G15" t="n">
-        <v>44.92812666666666</v>
+        <v>58.09981666666666</v>
       </c>
     </row>
     <row r="16">
@@ -882,10 +868,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>24.66666666666667</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
-        <v>92.99968666666666</v>
+        <v>122.7412966666667</v>
       </c>
     </row>
     <row r="17">
@@ -911,10 +897,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>15.66666666666667</v>
+        <v>19.66666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>43.83475333333333</v>
+        <v>66.66565333333334</v>
       </c>
     </row>
     <row r="18">
@@ -940,10 +926,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>50.66666666666666</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>124.9981266666667</v>
+        <v>133.8716033333334</v>
       </c>
     </row>
     <row r="19">
@@ -969,10 +955,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>40.66666666666666</v>
+        <v>45.33333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>62.18746000000001</v>
+        <v>68.79257333333332</v>
       </c>
     </row>
     <row r="20">
@@ -998,10 +984,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>283.2234933333334</v>
+        <v>663.5676500000001</v>
       </c>
     </row>
     <row r="21">
@@ -1027,10 +1013,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>56.03292000000001</v>
+        <v>52.05216333333333</v>
       </c>
     </row>
     <row r="22">
@@ -1056,10 +1042,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35.66666666666666</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="G22" t="n">
-        <v>87.74735666666668</v>
+        <v>111.7789166666667</v>
       </c>
     </row>
     <row r="23">
@@ -1085,10 +1071,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>37.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>70.16096333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1114,10 +1100,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>26.66666666666667</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>76.35146999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1143,10 +1129,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>29.14807333333333</v>
       </c>
     </row>
     <row r="26">
@@ -1172,10 +1158,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>35.66666666666666</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>15.64289666666667</v>
+        <v>47.29138666666666</v>
       </c>
     </row>
     <row r="27">
@@ -1201,10 +1187,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>17.33333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>25.73022</v>
+        <v>25.95256666666667</v>
       </c>
     </row>
     <row r="28">
@@ -1230,10 +1216,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11.66666666666667</v>
+        <v>15.66666666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>35.66387666666667</v>
+        <v>34.00460333333334</v>
       </c>
     </row>
     <row r="29">
@@ -1259,10 +1245,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>53.58646333333333</v>
+        <v>52.10580000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1288,25 +1274,39 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>22.66666666666667</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>66.65496999999999</v>
+        <v>52.83083666666666</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="A31" t="n">
+        <v>2023085</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N T Distributors</t>
+        </is>
+      </c>
       <c r="C31" t="n">
-        <v>200210502407</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+        <v>200405300324</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Food Mart</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>UDAY DILIP INDALKAR</t>
+        </is>
+      </c>
       <c r="F31" t="n">
-        <v>4.666666666666667</v>
+        <v>36</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>98.51073333333333</v>
       </c>
     </row>
     <row r="32">
@@ -1319,11 +1319,11 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>200405300324</v>
+        <v>200405300624</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Food Mart</t>
+          <t>DAILY NEEDS ENTERPRISES-2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1332,114 +1332,114 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>33</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="G32" t="n">
-        <v>67.55883333333334</v>
+        <v>208.18544</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2023085</v>
+        <v>2022939</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>Sunrise Enterprises</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>200405300624</v>
+        <v>200511800890</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DAILY NEEDS ENTERPRISES-2</t>
+          <t>Mahadev dairy</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>MOHD SHARIQUE KHAN</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>39.66666666666666</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="G33" t="n">
-        <v>168.4129533333333</v>
+        <v>107.8869266666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2022939</v>
+        <v>2005118</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>A1 DISTRIBUTOR</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>200511800890</v>
+        <v>200511801044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Mahadev dairy</t>
+          <t>DG MALL</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ROHAN SINGH</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>12.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
-        <v>49.70374</v>
+        <v>91.87452999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2005118</v>
+        <v>2023002</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A1 DISTRIBUTOR</t>
+          <t>Nimse Trading Company</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>200511801044</v>
+        <v>200625400127</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DG MALL</t>
+          <t>OM SUP. MARKET</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>AMIT SANJEEV PANDEY</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>33.33333333333334</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="G35" t="n">
-        <v>207.5623866666666</v>
+        <v>65.54083333333334</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2023002</v>
+        <v>2023823</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nimse Trading Company</t>
+          <t>Ashtavinayak Agencies</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>200625400127</v>
+        <v>200625400735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>OM SUP. MARKET</t>
+          <t>ROYAL SUPER MARKET</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1448,97 +1448,97 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10.33333333333333</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
-        <v>21.50418</v>
+        <v>35.51502</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2021125</v>
+        <v>2005118</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>N S Enterprises</t>
+          <t>A1 DISTRIBUTOR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>200625400735</v>
+        <v>200660400395</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ROYAL SUPER MARKET</t>
+          <t>KALWA SUPER MKT PVT LTD</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>ROHAN SINGH</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>13.33333333333333</v>
+        <v>21</v>
       </c>
       <c r="G37" t="n">
-        <v>9.259643333333335</v>
+        <v>29.01681666666667</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2005118</v>
+        <v>2022639</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A1 DISTRIBUTOR</t>
+          <t>Shivani Enterprises</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>200660400395</v>
+        <v>200923800009</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KALWA SUPER MKT PVT LTD</t>
+          <t>DARSHAN BISCUITS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>JOSHUA SHAJI FRANCIS</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>13.33333333333333</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="G38" t="n">
-        <v>36.10150333333333</v>
+        <v>316.9292133333333</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2022639</v>
+        <v>2009842</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>R. P. Agency</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200923800009</v>
+        <v>200984200153</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DARSHAN BISCUITS</t>
+          <t>SAI PRASAD DRY FRUIT</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>PRASAD PRADIPKUMAR RAUT</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>40.93277333333334</v>
       </c>
     </row>
     <row r="40">
@@ -1551,11 +1551,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>200984200153</v>
+        <v>200984200845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SAI PRASAD DRY FRUIT</t>
+          <t>WELCOME STORE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>38.66666666666666</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="G40" t="n">
-        <v>10.75553666666667</v>
+        <v>34.67592666666667</v>
       </c>
     </row>
     <row r="41">
@@ -1580,11 +1580,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>200984200845</v>
+        <v>200984201066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WELCOME STORE</t>
+          <t>ADIMAYA ENTERPRISES</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1593,39 +1593,39 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>20</v>
+        <v>32.33333333333334</v>
       </c>
       <c r="G41" t="n">
-        <v>18.51793</v>
+        <v>35.94880333333333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2009842</v>
+        <v>2023085</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R. P. Agency</t>
+          <t>N T Distributors</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>200984201066</v>
+        <v>201063400142</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ADIMAYA ENTERPRISES</t>
+          <t>TOWN BAZAAR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PRASAD PRADIPKUMAR RAUT</t>
+          <t>UDAY DILIP INDALKAR</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>21</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>11.26651333333333</v>
+        <v>92.34347000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1638,11 +1638,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>201063400142</v>
+        <v>201063400275</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TOWN BAZAAR</t>
+          <t>FOOD BASKET HK</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1651,39 +1651,39 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G43" t="n">
-        <v>78.63120333333335</v>
+        <v>102.4090866666667</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2023085</v>
+        <v>2023002</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>N T Distributors</t>
+          <t>Nimse Trading Company</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>201063400275</v>
+        <v>201074800326</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FOOD BASKET HK</t>
+          <t>Uma General Store</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UDAY DILIP INDALKAR</t>
+          <t>AMIT SANJEEV PANDEY</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G44" t="n">
-        <v>78.88364666666666</v>
+        <v>30.98505666666667</v>
       </c>
     </row>
     <row r="45">
@@ -1696,11 +1696,11 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>201074800326</v>
+        <v>201074800404</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Uma General Store</t>
+          <t>GURU KRIPA DAIRY  COLD DRINKS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1709,39 +1709,39 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>7.333333333333333</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="G45" t="n">
-        <v>16.91567666666667</v>
+        <v>56.46564333333333</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2023002</v>
+        <v>2011731</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nimse Trading Company</t>
+          <t>Sandeep Stores</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>201074800404</v>
+        <v>201173100172</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>GURU KRIPA DAIRY  COLD DRINKS</t>
+          <t>SHREE SADGURU KRUPA (NEW )</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AMIT SANJEEV PANDEY</t>
+          <t>SHUBHANGI RAIKWAR</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>8.666666666666666</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="G46" t="n">
-        <v>17.21250333333333</v>
+        <v>75.18834</v>
       </c>
     </row>
     <row r="47">
@@ -1754,11 +1754,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>201173100172</v>
+        <v>201173100249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SHREE SADGURU KRUPA (NEW )</t>
+          <t>ROYAL SUPER MARKET</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1767,39 +1767,39 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>19</v>
+        <v>30.66666666666667</v>
       </c>
       <c r="G47" t="n">
-        <v>19.30109666666667</v>
+        <v>140.0387133333333</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2011731</v>
+        <v>2018993</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sandeep Stores</t>
+          <t>SRI ENTERPRISES</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>201173100249</v>
+        <v>201178500076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ROYAL SUPER MARKET</t>
+          <t>B MART</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SHUBHANGI RAIKWAR</t>
+          <t>MOHD SHARIQUE KHAN</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G48" t="n">
-        <v>116.2644133333333</v>
+        <v>203.3141666666667</v>
       </c>
     </row>
     <row r="49">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>201178500076</v>
+        <v>201178500087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>B MART</t>
+          <t>V MART SUPER MARKET</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1825,39 +1825,39 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="G49" t="n">
-        <v>211.1102833333333</v>
+        <v>53.99136000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2018993</v>
+        <v>2022679</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>Shree Kulswamini Enterprises</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>201178500087</v>
+        <v>201294400165</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>V MART SUPER MARKET</t>
+          <t>B MART SUPER MARKET</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>ROHAN SINGH</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="G50" t="n">
-        <v>58.53358666666667</v>
+        <v>122.0849566666667</v>
       </c>
     </row>
     <row r="51">
@@ -1870,11 +1870,11 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>201294400165</v>
+        <v>201294400279</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>B MART SUPER MARKET</t>
+          <t>BALAJI FRESH MART</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>46</v>
+        <v>78.66666666666667</v>
       </c>
       <c r="G51" t="n">
-        <v>83.75323999999999</v>
+        <v>96.27256333333332</v>
       </c>
     </row>
     <row r="52">
@@ -1899,11 +1899,11 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>201294400279</v>
+        <v>201294400281</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BALAJI FRESH MART</t>
+          <t>SHREE BALAJI FOOD MALL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>45.33333333333334</v>
+        <v>73.66666666666667</v>
       </c>
       <c r="G52" t="n">
-        <v>83.11188</v>
+        <v>144.5002333333333</v>
       </c>
     </row>
     <row r="53">
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>201294400281</v>
+        <v>201294400288</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SHREE BALAJI FOOD MALL</t>
+          <t>B MART SUPER MARKET  (2)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1941,39 +1941,39 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>45.33333333333334</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="G53" t="n">
-        <v>153.32597</v>
+        <v>92.42781000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2022679</v>
+        <v>2022939</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shree Kulswamini Enterprises</t>
+          <t>Sunrise Enterprises</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>201294400288</v>
+        <v>201327000069</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B MART SUPER MARKET  (2)</t>
+          <t>PATEL KIRANA AND GENERAL STORES</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ROHAN SINGH</t>
+          <t>MOHD SHARIQUE KHAN</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>50.33333333333334</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>59.69597333333333</v>
+        <v>119.0924233333333</v>
       </c>
     </row>
     <row r="55">
@@ -1986,11 +1986,11 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>201327000069</v>
+        <v>201327000073</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PATEL KIRANA AND GENERAL STORES</t>
+          <t>TOWN BAZAAR</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>18.66666666666667</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>101.9252133333333</v>
+        <v>55.73072666666667</v>
       </c>
     </row>
     <row r="56">
@@ -2015,11 +2015,11 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>201327000073</v>
+        <v>201327000332</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TOWN BAZAAR</t>
+          <t>ASHAPURA MART</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2028,10 +2028,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>31.33333333333333</v>
+        <v>41</v>
       </c>
       <c r="G56" t="n">
-        <v>49.75285</v>
+        <v>62.44824333333333</v>
       </c>
     </row>
     <row r="57">
@@ -2044,11 +2044,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>201327000332</v>
+        <v>201327000363</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ASHAPURA MART</t>
+          <t>FINE FOOD BAZAAR</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2057,56 +2057,56 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>43.33333333333334</v>
+        <v>51.66666666666666</v>
       </c>
       <c r="G57" t="n">
-        <v>34.15892333333333</v>
+        <v>117.2941466666667</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2022939</v>
+        <v>2022639</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>Shivani Enterprises</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>201327000363</v>
+        <v>201330600206</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FINE FOOD BAZAAR</t>
+          <t>SAHAJANAND SUPER MARKET</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>JOSHUA SHAJI FRANCIS</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>52.33333333333334</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="G58" t="n">
-        <v>146.46358</v>
+        <v>28.85700666666667</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2022639</v>
+        <v>2023671</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Shivani Enterprises</t>
+          <t>Shamik Enterprises</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>201330600206</v>
+        <v>201330600340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SAHAJANAND SUPER MARKET</t>
+          <t>B MART</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2115,56 +2115,56 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>28.33333333333333</v>
+        <v>30.66666666666667</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>102.2013766666667</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2023303</v>
+        <v>2022939</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Krishna Marketing</t>
+          <t>Sunrise Enterprises</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>201330600340</v>
+        <v>201330600476</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>B MART</t>
+          <t>SHIVAM ENTERPRISES</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>MOHD SHARIQUE KHAN</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>13.66666666666667</v>
+        <v>45.66666666666666</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>117.4925266666667</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2022939</v>
+        <v>2018993</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Sunrise Enterprises</t>
+          <t>SRI ENTERPRISES</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>201330600476</v>
+        <v>201613300250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SHIVAM ENTERPRISES</t>
+          <t>SHREEHARI ENTERPRISES APNA BAZAR CO-OP</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>47.66666666666666</v>
+        <v>30</v>
       </c>
       <c r="G61" t="n">
-        <v>109.4187566666667</v>
+        <v>38.00519666666667</v>
       </c>
     </row>
     <row r="62">
@@ -2189,11 +2189,11 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>201613300250</v>
+        <v>201613300337</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>SHREEHARI ENTERPRISES APNA BAZAR CO-OP</t>
+          <t>A MART</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2202,112 +2202,112 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>30.33333333333333</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="G62" t="n">
-        <v>31.68701333333334</v>
+        <v>114.82037</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2018993</v>
+        <v>2023671</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SRI ENTERPRISES</t>
+          <t>Shamik Enterprises</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>201613300337</v>
+        <v>201624800468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A MART</t>
+          <t>KAVYA SUPER MARKET</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MOHD SHARIQUE KHAN</t>
+          <t>JOSHUA SHAJI FRANCIS</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>35.33333333333334</v>
+        <v>12</v>
       </c>
       <c r="G63" t="n">
-        <v>67.08329333333333</v>
+        <v>16.55300666666666</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="A64" t="n">
+        <v>2023671</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Shamik Enterprises</t>
+        </is>
+      </c>
       <c r="C64" t="n">
-        <v>201624800468</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+        <v>201624800522</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>BALAJI MART</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>JOSHUA SHAJI FRANCIS</t>
+        </is>
+      </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>40.33333333333334</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>80.87939</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2023303</v>
+        <v>2023085</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Krishna Marketing</t>
+          <t>N T Distributors</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>201624800522</v>
+        <v>201636400069</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BALAJI MART</t>
+          <t>JASMINE SUPER MARKET FOOD BASKET</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JOSHUA SHAJI FRANCIS</t>
+          <t>UDAY DILIP INDALKAR</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>16.66666666666667</v>
+        <v>51.33333333333334</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>66.39796</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>2023085</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>N T Distributors</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="n">
-        <v>201636400069</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>JASMINE SUPER MARKET FOOD BASKET</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>UDAY DILIP INDALKAR</t>
-        </is>
-      </c>
+        <v>201740900008</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>43.33333333333334</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="G66" t="n">
-        <v>81.97293000000001</v>
+        <v>16.47692</v>
       </c>
     </row>
     <row r="67">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>24.33333333333333</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="G67" t="n">
-        <v>37.89352666666667</v>
+        <v>52.21021666666667</v>
       </c>
     </row>
     <row r="68">
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>20</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="G68" t="n">
-        <v>28.33939666666667</v>
+        <v>32.73071333333333</v>
       </c>
     </row>
     <row r="69">
@@ -2391,19 +2391,19 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>36.66666666666666</v>
+        <v>43</v>
       </c>
       <c r="G69" t="n">
-        <v>86.13788333333332</v>
+        <v>95.73931666666665</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2021125</v>
+        <v>2023823</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N S Enterprises</t>
+          <t>Ashtavinayak Agencies</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>17.33333333333333</v>
+        <v>32.33333333333334</v>
       </c>
       <c r="G70" t="n">
-        <v>4.135126666666666</v>
+        <v>24.53345666666667</v>
       </c>
     </row>
     <row r="71">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>16.33333333333333</v>
+        <v>33.66666666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>36.30374333333334</v>
+        <v>75.98127333333333</v>
       </c>
     </row>
     <row r="72">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>41.66666666666666</v>
+        <v>43</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>102.3624333333333</v>
       </c>
     </row>
     <row r="73">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>44</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="G73" t="n">
-        <v>53.7176</v>
+        <v>82.78822</v>
       </c>
     </row>
     <row r="74">
@@ -2539,7 +2539,7 @@
         <v>24.33333333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>28.10231333333333</v>
+        <v>36.97863</v>
       </c>
     </row>
     <row r="75">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>15.66666666666667</v>
+        <v>14.66666666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>22.84453333333333</v>
+        <v>27.27785333333334</v>
       </c>
     </row>
     <row r="76">
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G76" t="n">
-        <v>24.54480333333333</v>
+        <v>26.15719333333334</v>
       </c>
     </row>
     <row r="77">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>22</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="G77" t="n">
-        <v>24.96948</v>
+        <v>27.17055</v>
       </c>
     </row>
     <row r="78">
@@ -2652,10 +2652,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G78" t="n">
-        <v>48.29786333333333</v>
+        <v>51.07444</v>
       </c>
     </row>
     <row r="79">
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>28.33333333333333</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="G79" t="n">
-        <v>66.37522</v>
+        <v>67.07551000000001</v>
       </c>
     </row>
     <row r="80">
@@ -2710,10 +2710,39 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>24.33333333333333</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="G80" t="n">
-        <v>41.3205</v>
+        <v>45.96094666666666</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2023823</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ashtavinayak Agencies</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>202382300072</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>RAJENDRA SALES</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AMIT SANJEEV PANDEY</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="G81" t="n">
+        <v>14.04947</v>
       </c>
     </row>
   </sheetData>
